--- a/branches/master/StructureDefinition-mii-lm-symptom.xlsx
+++ b/branches/master/StructureDefinition-mii-lm-symptom.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:35:53+00:00</t>
+    <t>2026-09-09T13:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-lm-symptom.xlsx
+++ b/branches/master/StructureDefinition-mii-lm-symptom.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:47:18+00:00</t>
+    <t>2026-09-11T09:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-lm-symptom.xlsx
+++ b/branches/master/StructureDefinition-mii-lm-symptom.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T09:58:18+00:00</t>
+    <t>2026-09-11T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
